--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.30_Q4_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.30_Q4_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02906083917483056</v>
+        <v>0.01695026515886861</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02906083917483056</v>
+        <v>0.01695026515886861</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.029030477668139</v>
+        <v>0.01692943848390388</v>
       </c>
       <c r="C3" t="n">
-        <v>0.029030477668139</v>
+        <v>0.01692943848390388</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0289744979533954</v>
+        <v>0.01689094047287158</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0289744979533954</v>
+        <v>0.01689094047287158</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02888402400179678</v>
+        <v>0.0168302138633214</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02888402400179678</v>
+        <v>0.0168302138633214</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02877177606681821</v>
+        <v>0.01675518657289178</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02877177606681821</v>
+        <v>0.01675518657289178</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02863858747666992</v>
+        <v>0.01666680045971693</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02863858747666992</v>
+        <v>0.01666680045971693</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02848314956322826</v>
+        <v>0.0165629072451735</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02848314956322826</v>
+        <v>0.0165629072451735</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02832013901846241</v>
+        <v>0.0164565323407966</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02832013901846241</v>
+        <v>0.0164565323407966</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02815011681417875</v>
+        <v>0.01634663860913482</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02815011681417875</v>
+        <v>0.01634663860913482</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02798105417880704</v>
+        <v>0.01623847185024423</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02798105417880704</v>
+        <v>0.01623847185024423</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02781794867313819</v>
+        <v>0.01613680540027474</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02781794867313819</v>
+        <v>0.01613680540027474</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.02767351500897499</v>
+        <v>0.01604649912038522</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02767351500897499</v>
+        <v>0.01604649912038522</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.02755148940217393</v>
+        <v>0.01597163799736943</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02755148940217393</v>
+        <v>0.01597163799736943</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.02745712462648164</v>
+        <v>0.01591472965830757</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02745712462648164</v>
+        <v>0.01591472965830757</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0273941675333564</v>
+        <v>0.01587879788669968</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0273941675333564</v>
+        <v>0.01587879788669968</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.02737072670861208</v>
+        <v>0.01586704341302049</v>
       </c>
       <c r="C17" t="n">
-        <v>0.02737072670861208</v>
+        <v>0.01586704341302049</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.02738858049659322</v>
+        <v>0.01588323190160205</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02738858049659322</v>
+        <v>0.01588323190160205</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.02745685912005036</v>
+        <v>0.01593137340876527</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02745685912005036</v>
+        <v>0.01593137340876527</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.02757918693312158</v>
+        <v>0.01601518394057407</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02757918693312158</v>
+        <v>0.01601518394057407</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.02779811885910989</v>
+        <v>0.01615597606889891</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02779811885910989</v>
+        <v>0.01615597606889891</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.02807047854476032</v>
+        <v>0.01633091818668875</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02807047854476032</v>
+        <v>0.01633091818668875</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.02839665606365164</v>
+        <v>0.01654049214639325</v>
       </c>
       <c r="C23" t="n">
-        <v>0.02839665606365164</v>
+        <v>0.01654049214639325</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.02881034407318823</v>
+        <v>0.01680092028128606</v>
       </c>
       <c r="C24" t="n">
-        <v>0.02881034407318823</v>
+        <v>0.01680092028128606</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.02929385262632658</v>
+        <v>0.01710396067543928</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02929385262632658</v>
+        <v>0.01710396067543928</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.02986271008055311</v>
+        <v>0.01746098328520488</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02986271008055311</v>
+        <v>0.01746098328520488</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.03052870412486591</v>
+        <v>0.01787631411545153</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03052870412486591</v>
+        <v>0.01787631411545153</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.03128513728799731</v>
+        <v>0.01834720558325012</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03128513728799731</v>
+        <v>0.01834720558325012</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.03213982103866567</v>
+        <v>0.01887629732378195</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03213982103866567</v>
+        <v>0.01887629732378195</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.03309506362932094</v>
+        <v>0.01946586280502394</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03309506362932094</v>
+        <v>0.01946586280502394</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.03415210158088017</v>
+        <v>0.02011710396697357</v>
       </c>
       <c r="C31" t="n">
-        <v>0.03415210158088017</v>
+        <v>0.02011710396697357</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
